--- a/bid/BID_COMPARISON.xlsx
+++ b/bid/BID_COMPARISON.xlsx
@@ -18,9 +18,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="$#,##0"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="11">
     <font>
       <name val="Calibri"/>
@@ -58,18 +56,18 @@
     </font>
     <font>
       <name val="Arial"/>
-      <sz val="10"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
       <color rgb="000000FF"/>
-      <sz val="10"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00C00000"/>
-      <sz val="10"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -78,7 +76,7 @@
     </font>
     <font>
       <name val="Arial"/>
-      <sz val="9"/>
+      <sz val="8"/>
     </font>
   </fonts>
   <fills count="7">
@@ -184,11 +182,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -200,10 +204,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -212,13 +216,9 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -587,40 +587,40 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="52" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>HVAC BID COMPARISON — 301 S Aztec Dr, White House TN 37188</t>
+          <t>HVAC BID COMPARISON  —  301 S Aztec Dr, White House TN 37188</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2.5-ton gas/electric package unit · R-454B · 995 CFM design airflow · quotes due Thu 2026-09-17 · printed 2026-09-17</t>
+          <t>2.5-ton gas/electric package unit · R-454B · 995 CFM design airflow · quotes due Thu 2026-09-17</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>LEGEND:  yellow = fill this in at the table   ·   blue text = taken from a written quote or email   ·   RED = hard requirement, a 'no' here disqualifies</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
+          <t>LEGEND:   yellow = fill in at the table    ·    blue = taken from a written quote or email    ·    RED = hard requirement, a 'no' disqualifies</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>REQUIREMENT</t>
@@ -681,32 +681,28 @@
           <t>Contact / title</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="B8" s="9" t="inlineStr"/>
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>Tyler O'Berry, Manager/Sales</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>Bill (Candy Faulkner, office)</t>
-        </is>
-      </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>Bill (office: Candy Faulkner)</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
         <is>
           <t>Aaron Lee</t>
         </is>
       </c>
-      <c r="F8" s="9" t="inlineStr">
+      <c r="F8" s="10" t="inlineStr">
         <is>
           <t>Mark / Daniel</t>
         </is>
       </c>
-      <c r="G8" s="10" t="inlineStr"/>
+      <c r="G8" s="9" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
@@ -714,25 +710,21 @@
           <t>Phone</t>
         </is>
       </c>
-      <c r="B9" s="10" t="inlineStr"/>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr"/>
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>Office (615) 757-5497
 Cell (629) 292-1310</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="D9" s="10" t="inlineStr">
         <is>
           <t>(615) 479-0886</t>
         </is>
       </c>
-      <c r="E9" s="10" t="inlineStr"/>
-      <c r="F9" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G9" s="10" t="inlineStr"/>
+      <c r="E9" s="9" t="inlineStr"/>
+      <c r="F9" s="9" t="inlineStr"/>
+      <c r="G9" s="9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
@@ -740,28 +732,28 @@
           <t>Email</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr"/>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="B10" s="9" t="inlineStr"/>
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>TOberry@petershvac.net</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="D10" s="10" t="inlineStr">
         <is>
           <t>bill.ghandc@gmail.com</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="E10" s="10" t="inlineStr">
         <is>
           <t>butleracservice@yahoo.com</t>
         </is>
       </c>
-      <c r="F10" s="9" t="inlineStr">
+      <c r="F10" s="10" t="inlineStr">
         <is>
           <t>info@huntertn.com</t>
         </is>
       </c>
-      <c r="G10" s="10" t="inlineStr"/>
+      <c r="G10" s="9" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
@@ -769,12 +761,16 @@
           <t>TN LICENSE NUMBER</t>
         </is>
       </c>
-      <c r="B11" s="10" t="inlineStr"/>
-      <c r="C11" s="10" t="inlineStr"/>
-      <c r="D11" s="10" t="inlineStr"/>
-      <c r="E11" s="10" t="inlineStr"/>
-      <c r="F11" s="10" t="inlineStr"/>
-      <c r="G11" s="10" t="inlineStr"/>
+      <c r="B11" s="9" t="inlineStr"/>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>#81099 - MECHANICAL</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr"/>
+      <c r="E11" s="9" t="inlineStr"/>
+      <c r="F11" s="9" t="inlineStr"/>
+      <c r="G11" s="9" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -795,33 +791,41 @@
           <t>Exact model number</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>Carrier 48NL-B300603</t>
         </is>
       </c>
-      <c r="C13" s="10" t="inlineStr"/>
-      <c r="D13" s="10" t="inlineStr"/>
-      <c r="E13" s="10" t="inlineStr"/>
-      <c r="F13" s="10" t="inlineStr"/>
-      <c r="G13" s="10" t="inlineStr"/>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>Carrier 48NL-B300603</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr"/>
+      <c r="E13" s="9" t="inlineStr"/>
+      <c r="F13" s="9" t="inlineStr"/>
+      <c r="G13" s="9" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>Tonnage / gas BTU in / BTU out</t>
-        </is>
-      </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>2.5 ton · 60,000 BTU</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="inlineStr"/>
-      <c r="D14" s="10" t="inlineStr"/>
-      <c r="E14" s="10" t="inlineStr"/>
-      <c r="F14" s="10" t="inlineStr"/>
-      <c r="G14" s="10" t="inlineStr"/>
+          <t>Tonnage / gas BTU input / output</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>2.5 ton - 60,000 BTU</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>2.5 ton - 60,000 BTU gas.  INPUT vs OUTPUT still not split</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr"/>
+      <c r="E14" s="9" t="inlineStr"/>
+      <c r="F14" s="9" t="inlineStr"/>
+      <c r="G14" s="9" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
@@ -829,41 +833,41 @@
           <t>SEER2</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>13.4</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>13.4 (single stage)</t>
-        </is>
-      </c>
-      <c r="D15" s="10" t="inlineStr"/>
-      <c r="E15" s="10" t="inlineStr"/>
-      <c r="F15" s="10" t="inlineStr"/>
-      <c r="G15" s="10" t="inlineStr"/>
-    </row>
-    <row r="16">
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>13.4</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr"/>
+      <c r="E15" s="9" t="inlineStr"/>
+      <c r="F15" s="9" t="inlineStr"/>
+      <c r="G15" s="9" t="inlineStr"/>
+    </row>
+    <row r="16" ht="40" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
           <t>Single stage or 2-stage</t>
         </is>
       </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>single</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>single — 2-stage adds $1,200–1,500</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="inlineStr"/>
-      <c r="E16" s="10" t="inlineStr"/>
-      <c r="F16" s="10" t="inlineStr"/>
-      <c r="G16" s="10" t="inlineStr"/>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>single, ECM blower.  The 15.2 SEER2 2-stage question is STILL UNANSWERED - no price, no recommendation</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr"/>
+      <c r="E16" s="9" t="inlineStr"/>
+      <c r="F16" s="9" t="inlineStr"/>
+      <c r="G16" s="9" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
@@ -871,118 +875,126 @@
           <t>Refrigerant</t>
         </is>
       </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>R-454B</t>
         </is>
       </c>
-      <c r="C17" s="10" t="inlineStr"/>
-      <c r="D17" s="10" t="inlineStr"/>
-      <c r="E17" s="10" t="inlineStr"/>
-      <c r="F17" s="10" t="inlineStr"/>
-      <c r="G17" s="10" t="inlineStr"/>
-    </row>
-    <row r="18">
+      <c r="C17" s="9" t="inlineStr"/>
+      <c r="D17" s="9" t="inlineStr"/>
+      <c r="E17" s="9" t="inlineStr"/>
+      <c r="F17" s="9" t="inlineStr"/>
+      <c r="G17" s="9" t="inlineStr"/>
+    </row>
+    <row r="18" ht="52" customHeight="1">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>HEAT EXCHANGER MATERIAL — MUST BE STAINLESS STEEL</t>
-        </is>
-      </c>
-      <c r="B18" s="9" t="inlineStr">
+          <t>HEAT EXCHANGER MATERIAL - MUST BE STAINLESS STEEL</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
         <is>
           <t>lifetime stainless</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr"/>
-      <c r="D18" s="10" t="inlineStr"/>
-      <c r="E18" s="10" t="inlineStr"/>
-      <c r="F18" s="10" t="inlineStr"/>
-      <c r="G18" s="10" t="inlineStr"/>
-    </row>
-    <row r="19">
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>STAINLESS STEEL, in writing TWICE: 'heat exchanger will be stainless steel per customer request' and 'LIFETIME HEAT EXCHANGER (STAINLESS STEEL)'</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr"/>
+      <c r="E18" s="9" t="inlineStr"/>
+      <c r="F18" s="9" t="inlineStr"/>
+      <c r="G18" s="9" t="inlineStr"/>
+    </row>
+    <row r="19" ht="34" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>Heat exchanger warranty term</t>
-        </is>
-      </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>lifetime (register within 90 days or drops to 20 yr)</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>'lifetime' — material NOT stated in writing</t>
-        </is>
-      </c>
-      <c r="D19" s="10" t="inlineStr"/>
-      <c r="E19" s="10" t="inlineStr"/>
-      <c r="F19" s="10" t="inlineStr"/>
-      <c r="G19" s="10" t="inlineStr"/>
+          <t>Heat exchanger / parts / compressor warranty</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>lifetime HX (register in 90 days or drops to 20 yr)</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>LIFETIME HX + 10 yr parts + 10 yr compressor</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr"/>
+      <c r="E19" s="9" t="inlineStr"/>
+      <c r="F19" s="9" t="inlineStr"/>
+      <c r="G19" s="9" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>Labor warranty — term</t>
-        </is>
-      </c>
-      <c r="B20" s="9" t="inlineStr">
+          <t>Labor warranty - term</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
         <is>
           <t>10 yr</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>2 yr workmanship</t>
-        </is>
-      </c>
-      <c r="D20" s="10" t="inlineStr"/>
-      <c r="E20" s="10" t="inlineStr"/>
-      <c r="F20" s="10" t="inlineStr"/>
-      <c r="G20" s="10" t="inlineStr"/>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>5 yr INCLUDED (was 2 yr on the first proposal)</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr"/>
+      <c r="E20" s="9" t="inlineStr"/>
+      <c r="F20" s="9" t="inlineStr"/>
+      <c r="G20" s="9" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>Labor warranty — cost</t>
-        </is>
-      </c>
-      <c r="B21" s="9" t="inlineStr">
+          <t>Labor warranty - cost to reach 10 yr</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
         <is>
           <t>$800</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>cost to extend to 10 yr = ?</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="inlineStr"/>
-      <c r="E21" s="10" t="inlineStr"/>
-      <c r="F21" s="10" t="inlineStr"/>
-      <c r="G21" s="10" t="inlineStr"/>
-    </row>
-    <row r="22">
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>+$500.00</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr"/>
+      <c r="E21" s="9" t="inlineStr"/>
+      <c r="F21" s="9" t="inlineStr"/>
+      <c r="G21" s="9" t="inlineStr"/>
+    </row>
+    <row r="22" ht="34" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>Labor warranty — what it covers</t>
-        </is>
-      </c>
-      <c r="B22" s="9" t="inlineStr">
+          <t>Labor warranty - what it covers</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
         <is>
           <t>all labour + freon</t>
         </is>
       </c>
-      <c r="C22" s="10" t="inlineStr"/>
-      <c r="D22" s="10" t="inlineStr"/>
-      <c r="E22" s="10" t="inlineStr"/>
-      <c r="F22" s="10" t="inlineStr"/>
-      <c r="G22" s="10" t="inlineStr"/>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>all labour on warranty parts repairs, priority service, discounted maintenance</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr"/>
+      <c r="E22" s="9" t="inlineStr"/>
+      <c r="F22" s="9" t="inlineStr"/>
+      <c r="G22" s="9" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>DUCTWORK — every item below is IN the price</t>
+          <t>DUCTWORK - every item below is IN the price</t>
         </is>
       </c>
       <c r="B23" s="6" t="n"/>
@@ -992,69 +1004,81 @@
       <c r="F23" s="6" t="n"/>
       <c r="G23" s="7" t="n"/>
     </row>
-    <row r="24">
+    <row r="24" ht="52" customHeight="1">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>1. Twist at unit REMOVED, new square-to-round transitions on BOTH supply and return</t>
-        </is>
-      </c>
-      <c r="B24" s="9" t="inlineStr">
+          <t>1. Twist at unit REMOVED, new square-to-round on BOTH supply and return</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
         <is>
           <t>included</t>
         </is>
       </c>
-      <c r="C24" s="10" t="inlineStr"/>
-      <c r="D24" s="10" t="inlineStr"/>
-      <c r="E24" s="10" t="inlineStr"/>
-      <c r="F24" s="10" t="inlineStr"/>
-      <c r="G24" s="10" t="inlineStr"/>
-    </row>
-    <row r="25">
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>YES - 'run the new R/A trunk in a strait shot to ELIMINATE the existing cross over/twist' + square-to-round take-offs on BOTH return and supply</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr"/>
+      <c r="E24" s="9" t="inlineStr"/>
+      <c r="F24" s="9" t="inlineStr"/>
+      <c r="G24" s="9" t="inlineStr"/>
+    </row>
+    <row r="25" ht="34" customHeight="1">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>2. Dining / master / living upgraded 6" → 8" (saddle tap + balancing damper + boot)</t>
-        </is>
-      </c>
-      <c r="B25" s="10" t="inlineStr"/>
-      <c r="C25" s="10" t="inlineStr"/>
-      <c r="D25" s="10" t="inlineStr"/>
-      <c r="E25" s="10" t="inlineStr"/>
-      <c r="F25" s="10" t="inlineStr"/>
-      <c r="G25" s="10" t="inlineStr"/>
-    </row>
-    <row r="26">
+          <t>2. Dining / master / living upgraded 6" to 8" (saddle tap, damper, boot)</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr"/>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>YES - all three, with dampers on every new/modified lead for balancing</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr"/>
+      <c r="E25" s="9" t="inlineStr"/>
+      <c r="F25" s="9" t="inlineStr"/>
+      <c r="G25" s="9" t="inlineStr"/>
+    </row>
+    <row r="26" ht="52" customHeight="1">
       <c r="A26" s="8" t="inlineStr">
         <is>
           <t>3. New 7" run to garage, cored through brick and sealed, brown register</t>
         </is>
       </c>
-      <c r="B26" s="10" t="inlineStr"/>
-      <c r="C26" s="10" t="inlineStr"/>
-      <c r="D26" s="10" t="inlineStr"/>
-      <c r="E26" s="9" t="inlineStr">
-        <is>
-          <t>REFUSES — says branch duct to garage violates code (fume backfeed)</t>
-        </is>
-      </c>
-      <c r="F26" s="10" t="inlineStr"/>
-      <c r="G26" s="10" t="inlineStr"/>
-    </row>
-    <row r="27">
+      <c r="B26" s="9" t="inlineStr"/>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>YES - 7" lead + a few ft of 12" hard pipe, chased through the brick, metal critter guard inside the crawlspace</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr"/>
+      <c r="E26" s="10" t="inlineStr">
+        <is>
+          <t>REFUSES - says a branch duct into a garage violates code (fume backfeed) and they will not do the job</t>
+        </is>
+      </c>
+      <c r="F26" s="9" t="inlineStr"/>
+      <c r="G26" s="9" t="inlineStr"/>
+    </row>
+    <row r="27" ht="40" customHeight="1">
       <c r="A27" s="8" t="inlineStr">
         <is>
           <t>4. New 16" return with BOTH sheet-metal 90s</t>
         </is>
       </c>
-      <c r="B27" s="10" t="inlineStr"/>
-      <c r="C27" s="9" t="inlineStr">
-        <is>
-          <t>quoted 16" FLEX with two 16" 90s — sheet metal not confirmed</t>
-        </is>
-      </c>
-      <c r="D27" s="10" t="inlineStr"/>
-      <c r="E27" s="10" t="inlineStr"/>
-      <c r="F27" s="10" t="inlineStr"/>
-      <c r="G27" s="10" t="inlineStr"/>
+      <c r="B27" s="9" t="inlineStr"/>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>PARTIAL - the (2) 16" 90s ARE galvanized sheet metal, but the TRUNK is 16" FLEX, not sheet metal</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr"/>
+      <c r="E27" s="9" t="inlineStr"/>
+      <c r="F27" s="9" t="inlineStr"/>
+      <c r="G27" s="9" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
@@ -1062,89 +1086,105 @@
           <t>4b. 18" return priced as a SEPARATE option</t>
         </is>
       </c>
-      <c r="B28" s="10" t="inlineStr"/>
-      <c r="C28" s="10" t="inlineStr"/>
-      <c r="D28" s="10" t="inlineStr"/>
-      <c r="E28" s="10" t="inlineStr"/>
-      <c r="F28" s="10" t="inlineStr"/>
-      <c r="G28" s="10" t="inlineStr"/>
+      <c r="B28" s="9" t="inlineStr"/>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>+$160.00</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr"/>
+      <c r="E28" s="9" t="inlineStr"/>
+      <c r="F28" s="9" t="inlineStr"/>
+      <c r="G28" s="9" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>5. Return filter grille 20x25 STAYS — no grille change</t>
-        </is>
-      </c>
-      <c r="B29" s="9" t="inlineStr">
-        <is>
-          <t>n/a — stays</t>
-        </is>
-      </c>
-      <c r="C29" s="10" t="inlineStr"/>
-      <c r="D29" s="10" t="inlineStr"/>
-      <c r="E29" s="10" t="inlineStr"/>
-      <c r="F29" s="10" t="inlineStr"/>
-      <c r="G29" s="10" t="inlineStr"/>
-    </row>
-    <row r="30">
+          <t>5. Return filter grille 20x25 STAYS</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>n/a - stays</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>stays, plus 6 months of 20x25x1 pleated filters free</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr"/>
+      <c r="E29" s="9" t="inlineStr"/>
+      <c r="F29" s="9" t="inlineStr"/>
+      <c r="G29" s="9" t="inlineStr"/>
+    </row>
+    <row r="30" ht="52" customHeight="1">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>6. Existing duct inspected, re-strapped, sealed/taped (NOT replaced for damp insulation)</t>
-        </is>
-      </c>
-      <c r="B30" s="10" t="inlineStr"/>
-      <c r="C30" s="10" t="inlineStr"/>
-      <c r="D30" s="10" t="inlineStr"/>
-      <c r="E30" s="10" t="inlineStr"/>
-      <c r="F30" s="10" t="inlineStr"/>
-      <c r="G30" s="10" t="inlineStr"/>
-    </row>
-    <row r="31">
+          <t>6. Existing duct inspected, re-strapped, sealed (NOT replaced for damp insulation)</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr"/>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>YES - full mastic seal, mastic-backed metal tape, re-strapped high and tight, NEW sheet metal return panning sealed + insulated, return cavity sealed, microbial spray</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr"/>
+      <c r="E30" s="9" t="inlineStr"/>
+      <c r="F30" s="9" t="inlineStr"/>
+      <c r="G30" s="9" t="inlineStr"/>
+    </row>
+    <row r="31" ht="40" customHeight="1">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>7. Unit base closed off at pad — rodent / snake / weather, incl. base closure panel</t>
-        </is>
-      </c>
-      <c r="B31" s="10" t="inlineStr"/>
-      <c r="C31" s="10" t="inlineStr"/>
-      <c r="D31" s="10" t="inlineStr"/>
-      <c r="E31" s="10" t="inlineStr"/>
-      <c r="F31" s="10" t="inlineStr"/>
-      <c r="G31" s="10" t="inlineStr"/>
-    </row>
-    <row r="32">
+          <t>7. Unit base closed off at the pad - rodent / snake / weather</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="inlineStr"/>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>YES - new shroud, critter guards, sealed to the structure, PVC drain with P-trap, new plastic pad</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr"/>
+      <c r="E31" s="9" t="inlineStr"/>
+      <c r="F31" s="9" t="inlineStr"/>
+      <c r="G31" s="9" t="inlineStr"/>
+    </row>
+    <row r="32" ht="34" customHeight="1">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>8. UVC REKO R2000 (Jeff supplies) installed + wired, no extra labour, lamps facing coil</t>
-        </is>
-      </c>
-      <c r="B32" s="10" t="inlineStr"/>
-      <c r="C32" s="9" t="inlineStr">
-        <is>
-          <t>YES — no additional cost, added to scope</t>
-        </is>
-      </c>
-      <c r="D32" s="10" t="inlineStr"/>
-      <c r="E32" s="10" t="inlineStr"/>
-      <c r="F32" s="10" t="inlineStr"/>
-      <c r="G32" s="10" t="inlineStr"/>
-    </row>
-    <row r="33">
+          <t>8. UVC REKO R2000 (Jeff supplies) installed + wired, lamps facing coil, no extra labour</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="inlineStr"/>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>YES - installed facing the coil, NO additional charge</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr"/>
+      <c r="E32" s="9" t="inlineStr"/>
+      <c r="F32" s="9" t="inlineStr"/>
+      <c r="G32" s="9" t="inlineStr"/>
+    </row>
+    <row r="33" ht="40" customHeight="1">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>9. ecobee EB-STATE6P-01 (Jeff supplies): NEW 18 AWG + C wire, install + start-up</t>
-        </is>
-      </c>
-      <c r="B33" s="10" t="inlineStr"/>
-      <c r="C33" s="9" t="inlineStr">
-        <is>
-          <t>18/8 wire pull $295 — install/startup not priced</t>
-        </is>
-      </c>
-      <c r="D33" s="10" t="inlineStr"/>
-      <c r="E33" s="10" t="inlineStr"/>
-      <c r="F33" s="10" t="inlineStr"/>
-      <c r="G33" s="10" t="inlineStr"/>
+          <t>9. ecobee EB-STATE6P-01 (Jeff supplies): new 18 AWG + C wire, install + start-up</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="inlineStr"/>
+      <c r="C33" s="10" t="inlineStr">
+        <is>
+          <t>YES - install, set-up AND programming at no cost. 18/8 wire pull is $295</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr"/>
+      <c r="E33" s="9" t="inlineStr"/>
+      <c r="F33" s="9" t="inlineStr"/>
+      <c r="G33" s="9" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
@@ -1165,12 +1205,16 @@
           <t>Ductwork itemised on the quote</t>
         </is>
       </c>
-      <c r="B35" s="10" t="inlineStr"/>
-      <c r="C35" s="10" t="inlineStr"/>
-      <c r="D35" s="10" t="inlineStr"/>
-      <c r="E35" s="10" t="inlineStr"/>
-      <c r="F35" s="10" t="inlineStr"/>
-      <c r="G35" s="10" t="inlineStr"/>
+      <c r="B35" s="9" t="inlineStr"/>
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t>YES - 3-page proposal with a full line-item breakdown</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr"/>
+      <c r="E35" s="9" t="inlineStr"/>
+      <c r="F35" s="9" t="inlineStr"/>
+      <c r="G35" s="9" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
@@ -1178,12 +1222,12 @@
           <t>Price per linear foot</t>
         </is>
       </c>
-      <c r="B36" s="10" t="inlineStr"/>
-      <c r="C36" s="10" t="inlineStr"/>
-      <c r="D36" s="10" t="inlineStr"/>
-      <c r="E36" s="10" t="inlineStr"/>
-      <c r="F36" s="10" t="inlineStr"/>
-      <c r="G36" s="10" t="inlineStr"/>
+      <c r="B36" s="9" t="inlineStr"/>
+      <c r="C36" s="9" t="inlineStr"/>
+      <c r="D36" s="9" t="inlineStr"/>
+      <c r="E36" s="9" t="inlineStr"/>
+      <c r="F36" s="9" t="inlineStr"/>
+      <c r="G36" s="9" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
@@ -1191,29 +1235,33 @@
           <t>Permit included</t>
         </is>
       </c>
-      <c r="B37" s="10" t="inlineStr"/>
-      <c r="C37" s="10" t="inlineStr"/>
-      <c r="D37" s="10" t="inlineStr"/>
-      <c r="E37" s="10" t="inlineStr"/>
-      <c r="F37" s="10" t="inlineStr"/>
-      <c r="G37" s="10" t="inlineStr"/>
-    </row>
-    <row r="38">
+      <c r="B37" s="9" t="inlineStr"/>
+      <c r="C37" s="10" t="inlineStr">
+        <is>
+          <t>$95.00</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr"/>
+      <c r="E37" s="9" t="inlineStr"/>
+      <c r="F37" s="9" t="inlineStr"/>
+      <c r="G37" s="9" t="inlineStr"/>
+    </row>
+    <row r="38" ht="40" customHeight="1">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>Start-up readings ON THE INVOICE: supply + return static pressure, airflow set to 995 CFM</t>
-        </is>
-      </c>
-      <c r="B38" s="10" t="inlineStr"/>
-      <c r="C38" s="9" t="inlineStr">
-        <is>
-          <t>yes — static pressure at completion</t>
-        </is>
-      </c>
-      <c r="D38" s="10" t="inlineStr"/>
-      <c r="E38" s="10" t="inlineStr"/>
-      <c r="F38" s="10" t="inlineStr"/>
-      <c r="G38" s="10" t="inlineStr"/>
+          <t>Start-up readings ON THE INVOICE: static pressure + airflow set to 995 CFM</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="inlineStr"/>
+      <c r="C38" s="10" t="inlineStr">
+        <is>
+          <t>Static pressure recorded at completion.  '995 CFM' appears NOWHERE in the document</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr"/>
+      <c r="E38" s="9" t="inlineStr"/>
+      <c r="F38" s="9" t="inlineStr"/>
+      <c r="G38" s="9" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
@@ -1221,12 +1269,12 @@
           <t>How soon could you start</t>
         </is>
       </c>
-      <c r="B39" s="10" t="inlineStr"/>
-      <c r="C39" s="10" t="inlineStr"/>
-      <c r="D39" s="10" t="inlineStr"/>
-      <c r="E39" s="10" t="inlineStr"/>
-      <c r="F39" s="10" t="inlineStr"/>
-      <c r="G39" s="10" t="inlineStr"/>
+      <c r="B39" s="9" t="inlineStr"/>
+      <c r="C39" s="9" t="inlineStr"/>
+      <c r="D39" s="9" t="inlineStr"/>
+      <c r="E39" s="9" t="inlineStr"/>
+      <c r="F39" s="9" t="inlineStr"/>
+      <c r="G39" s="9" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
@@ -1247,12 +1295,20 @@
           <t>Equipment + install</t>
         </is>
       </c>
-      <c r="B41" s="10" t="inlineStr"/>
-      <c r="C41" s="10" t="inlineStr"/>
-      <c r="D41" s="10" t="inlineStr"/>
-      <c r="E41" s="10" t="inlineStr"/>
-      <c r="F41" s="10" t="inlineStr"/>
-      <c r="G41" s="10" t="inlineStr"/>
+      <c r="B41" s="10" t="inlineStr">
+        <is>
+          <t>$8,200</t>
+        </is>
+      </c>
+      <c r="C41" s="10" t="inlineStr">
+        <is>
+          <t>$8,520.00</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="inlineStr"/>
+      <c r="E41" s="9" t="inlineStr"/>
+      <c r="F41" s="9" t="inlineStr"/>
+      <c r="G41" s="9" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
@@ -1260,25 +1316,41 @@
           <t>Ductwork</t>
         </is>
       </c>
-      <c r="B42" s="10" t="inlineStr"/>
-      <c r="C42" s="10" t="inlineStr"/>
-      <c r="D42" s="10" t="inlineStr"/>
-      <c r="E42" s="10" t="inlineStr"/>
-      <c r="F42" s="10" t="inlineStr"/>
-      <c r="G42" s="10" t="inlineStr"/>
-    </row>
-    <row r="43">
+      <c r="B42" s="10" t="inlineStr">
+        <is>
+          <t>included in $9,000</t>
+        </is>
+      </c>
+      <c r="C42" s="10" t="inlineStr">
+        <is>
+          <t>$2,750.00</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="inlineStr"/>
+      <c r="E42" s="9" t="inlineStr"/>
+      <c r="F42" s="9" t="inlineStr"/>
+      <c r="G42" s="9" t="inlineStr"/>
+    </row>
+    <row r="43" ht="34" customHeight="1">
       <c r="A43" s="8" t="inlineStr">
         <is>
           <t>Options / add-ons</t>
         </is>
       </c>
-      <c r="B43" s="10" t="inlineStr"/>
-      <c r="C43" s="10" t="inlineStr"/>
-      <c r="D43" s="10" t="inlineStr"/>
-      <c r="E43" s="10" t="inlineStr"/>
-      <c r="F43" s="10" t="inlineStr"/>
-      <c r="G43" s="10" t="inlineStr"/>
+      <c r="B43" s="10" t="inlineStr">
+        <is>
+          <t>+$800 = 10-yr labour &amp; freon</t>
+        </is>
+      </c>
+      <c r="C43" s="10" t="inlineStr">
+        <is>
+          <t>+$500 10-yr labour | +$160 18" return | -$300 TVA rebate</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="inlineStr"/>
+      <c r="E43" s="9" t="inlineStr"/>
+      <c r="F43" s="9" t="inlineStr"/>
+      <c r="G43" s="9" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="12" t="inlineStr">
@@ -1286,64 +1358,96 @@
           <t>TOTAL DELIVERED</t>
         </is>
       </c>
-      <c r="B44" s="13" t="inlineStr">
-        <is>
-          <t>$9,000</t>
-        </is>
-      </c>
-      <c r="C44" s="14" t="inlineStr"/>
-      <c r="D44" s="14" t="inlineStr"/>
-      <c r="E44" s="14" t="inlineStr"/>
-      <c r="F44" s="14" t="inlineStr"/>
-      <c r="G44" s="14" t="inlineStr"/>
+      <c r="B44" s="12" t="inlineStr">
+        <is>
+          <t>$9,000 delivered</t>
+        </is>
+      </c>
+      <c r="C44" s="12" t="inlineStr">
+        <is>
+          <t>$11,270.00  (8,520 + 2,750)</t>
+        </is>
+      </c>
+      <c r="D44" s="13" t="inlineStr"/>
+      <c r="E44" s="13" t="inlineStr"/>
+      <c r="F44" s="13" t="inlineStr"/>
+      <c r="G44" s="13" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="15" t="inlineStr">
-        <is>
-          <t>NOTES / RED FLAGS</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="26" customHeight="1">
-      <c r="A47" s="16" t="inlineStr">
-        <is>
-          <t>• Benchmark to beat: Daniels, Carrier 48NL-B300603, $9,000 delivered = unit $8,200 + $800 for 10-yr labour AND freon, twist fix and new supply/return flex included.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="26" customHeight="1">
-      <c r="A48" s="16" t="inlineStr">
-        <is>
-          <t>• STILL OWED BY DANIELS (logged 2026-09-10, still open): the flex diameters IN WRITING. The revised proposal deleted the 16" flex supply/return, the 16"-14" reducer and the 875 CFM line. That connection work is the whole reason $9,000 counts as turnkey.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="26" customHeight="1">
-      <c r="A49" s="16" t="inlineStr">
-        <is>
-          <t>• Peters sent a REVISED proposal 2026-09-17 09:13 AM (attachment: 'JEFF LOEWEN REPLACEMENT CARRIER WITH DUCTING 2.pdf') — figures above are from the FIRST proposal and Jeff's follow-up. Update this sheet from the revised PDF.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="26" customHeight="1">
-      <c r="A50" s="16" t="inlineStr">
-        <is>
-          <t>• Butler will not quote the garage duct at all. If the garage run matters, Butler is not comparable on scope.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="26" customHeight="1">
-      <c r="A51" s="16" t="inlineStr">
-        <is>
-          <t>• Never reached by email — phone only: Covenant H&amp;C (615) 829-9699 · Brown &amp; Son / hbrownhvac (615) 325-2624.</t>
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>READ THIS BEFORE COMPARING THE TOTALS</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="n"/>
+      <c r="C46" s="6" t="n"/>
+      <c r="D46" s="6" t="n"/>
+      <c r="E46" s="6" t="n"/>
+      <c r="F46" s="6" t="n"/>
+      <c r="G46" s="7" t="n"/>
+    </row>
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="14" t="inlineStr">
+        <is>
+          <t>- THE TWO TOTALS ARE NOT THE SAME JOB. Daniels' $9,000 covers the unit, the twist fix and new supply/return flex. Peters' $11,270 ALSO includes three 6"-to-8" branch upgrades, the 7" garage run, a new 16" return trunk with sheet-metal 90s, a full mastic duct seal, new sheet metal return panning, microbial treatment, the permit and six months of filters. Compare scope before price.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="30" customHeight="1">
+      <c r="A48" s="14" t="inlineStr">
+        <is>
+          <t>- Peters has NO printed grand total. $11,270.00 is arithmetic, and it checks two independent ways: 8,520 + 2,750 = 11,270, and the page-3 breakdown (6,260 unit w/ pad + 2,470 labour + 1,475 ducting materials + 325 duct seal + 350 misc + 95 permit + 295 t-stat wire) sums to exactly 11,270. Both sections state the total includes all sales tax.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="30" customHeight="1">
+      <c r="A49" s="14" t="inlineStr">
+        <is>
+          <t>- LIKE FOR LIKE ON LABOUR: Daniels $9,000 already has 10-yr labour+freon. Peters needs +$500 to reach 10 yr, so the comparable Peters figure is $11,770 before the -$300 TVA rebate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="30" customHeight="1">
+      <c r="A50" s="14" t="inlineStr">
+        <is>
+          <t>- STILL OWED BY DANIELS, logged 2026-09-10 and still open: the flex diameters IN WRITING. The revised proposal deleted the 16" flex supply/return, the 16"-14" reducer and the 875 CFM line. That connection work is the entire reason $9,000 counts as turnkey. Do not sign without it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="30" customHeight="1">
+      <c r="A51" s="14" t="inlineStr">
+        <is>
+          <t>- STILL OWED BY PETERS: the 15.2 SEER2 two-stage price and his recommendation (asked, not answered); gas BTU input vs output; and whether the 16" return TRUNK can be sheet metal rather than flex.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="30" customHeight="1">
+      <c r="A52" s="14" t="inlineStr">
+        <is>
+          <t>- MINOR BUT IT IS IN THE CONTRACT YOU WOULD SIGN: Peters' 'Notice to Owner' boilerplate cites MISSOURI lien law (Chapter 429, RSMO) in a Tennessee contract. Almost certainly a template leftover - worth one question.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="30" customHeight="1">
+      <c r="A53" s="14" t="inlineStr">
+        <is>
+          <t>- Peters proposal dated 9/17/2026, valid 90 days, prepared by Tyler O'Berry. Payment due 30 days after completion; 2% surcharge on card payments of $1,000 or more.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="30" customHeight="1">
+      <c r="A54" s="14" t="inlineStr">
+        <is>
+          <t>- Carrier lifetime stainless heat exchanger must be REGISTERED WITHIN 90 DAYS of install or it drops to 20 years.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="17">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A40:G40"/>
     <mergeCell ref="A51:G51"/>
+    <mergeCell ref="A53:G53"/>
     <mergeCell ref="A34:G34"/>
     <mergeCell ref="A12:G12"/>
     <mergeCell ref="A4:G4"/>
@@ -1351,12 +1455,14 @@
     <mergeCell ref="A48:G48"/>
     <mergeCell ref="A50:G50"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A54:G54"/>
+    <mergeCell ref="A52:G52"/>
     <mergeCell ref="A7:G7"/>
     <mergeCell ref="A49:G49"/>
     <mergeCell ref="A47:G47"/>
     <mergeCell ref="A23:G23"/>
   </mergeCells>
-  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <pageMargins left="0.25" right="0.25" top="0.35" bottom="0.35" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>